--- a/Project/LuckyFruits/server/Surface/LuckyFruitsCore.xlsx
+++ b/Project/LuckyFruits/server/Surface/LuckyFruitsCore.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Project\LuckyFruits\server\Surface\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Project\_tmp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE420D61-0200-4271-B09D-E947A11F2D08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8D1F85B6-D514-4EDD-AC00-BC53CD7544A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2505" yWindow="1560" windowWidth="21600" windowHeight="13365" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4110" yWindow="2235" windowWidth="21600" windowHeight="13365" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LuckyFruitsCore" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="39">
   <si>
     <t>编号【KEY】</t>
   </si>
@@ -134,7 +134,9 @@
   </si>
   <si>
     <t>红霉运</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>float</t>
   </si>
 </sst>
 </file>
@@ -253,7 +255,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -273,7 +275,10 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="6" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -596,7 +601,7 @@
         <v>19</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="I3" s="7" t="s">
         <v>18</v>
@@ -661,7 +666,9 @@
       </c>
     </row>
     <row r="6" spans="1:9" ht="21.95" customHeight="1">
-      <c r="A6" s="4"/>
+      <c r="A6" s="4">
+        <v>0</v>
+      </c>
       <c r="B6" s="4" t="s">
         <v>22</v>
       </c>
@@ -693,8 +700,8 @@
       <c r="G7" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="H7" s="5">
-        <v>1</v>
+      <c r="H7" s="12">
+        <v>8.69</v>
       </c>
       <c r="I7" s="8">
         <v>2</v>
@@ -712,8 +719,8 @@
       <c r="G8" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="H8" s="9">
-        <v>2</v>
+      <c r="H8" s="13">
+        <v>8.7100000000000009</v>
       </c>
       <c r="I8" s="10">
         <v>2</v>
@@ -731,8 +738,8 @@
       <c r="G9" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="H9" s="9">
-        <v>2</v>
+      <c r="H9" s="13">
+        <v>8.5500000000000007</v>
       </c>
       <c r="I9" s="10">
         <v>2</v>
@@ -750,8 +757,8 @@
       <c r="G10" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="H10" s="9">
-        <v>2</v>
+      <c r="H10" s="13">
+        <v>8.7100000000000009</v>
       </c>
       <c r="I10" s="10">
         <v>2</v>
@@ -769,8 +776,8 @@
       <c r="G11" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="H11" s="9">
-        <v>1</v>
+      <c r="H11" s="13">
+        <v>24.22</v>
       </c>
       <c r="I11" s="10">
         <v>3</v>
@@ -788,8 +795,8 @@
       <c r="G12" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="H12" s="9">
-        <v>2</v>
+      <c r="H12" s="13">
+        <v>12.13</v>
       </c>
       <c r="I12" s="10">
         <v>6</v>
@@ -807,8 +814,8 @@
       <c r="G13" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="H13" s="9">
-        <v>2</v>
+      <c r="H13" s="13">
+        <v>8.93</v>
       </c>
       <c r="I13" s="10">
         <v>8</v>
@@ -826,8 +833,8 @@
       <c r="G14" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H14" s="9">
-        <v>2</v>
+      <c r="H14" s="13">
+        <v>6.07</v>
       </c>
       <c r="I14" s="10">
         <v>12</v>
@@ -845,8 +852,8 @@
       <c r="G15" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="H15" s="9">
-        <v>2</v>
+      <c r="H15" s="13">
+        <v>2.79</v>
       </c>
       <c r="I15" s="10">
         <v>30</v>
@@ -864,8 +871,8 @@
       <c r="G16" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="H16" s="9">
-        <v>1</v>
+      <c r="H16" s="13">
+        <v>0.5</v>
       </c>
       <c r="I16" s="10"/>
     </row>
@@ -881,8 +888,8 @@
       <c r="G17" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="H17" s="9">
-        <v>1</v>
+      <c r="H17" s="13">
+        <v>0.3</v>
       </c>
       <c r="I17" s="10"/>
     </row>
@@ -898,8 +905,8 @@
       <c r="G18" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="H18" s="9">
-        <v>1</v>
+      <c r="H18" s="13">
+        <v>0.3</v>
       </c>
       <c r="I18" s="10"/>
     </row>
@@ -915,8 +922,8 @@
       <c r="G19" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="H19" s="9">
-        <v>1</v>
+      <c r="H19" s="13">
+        <v>0.1</v>
       </c>
       <c r="I19" s="10"/>
     </row>
@@ -932,8 +939,8 @@
       <c r="G20" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="H20" s="9">
-        <v>1</v>
+      <c r="H20" s="13">
+        <v>5</v>
       </c>
       <c r="I20" s="10"/>
     </row>
@@ -949,8 +956,8 @@
       <c r="G21" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="H21" s="11">
-        <v>1</v>
+      <c r="H21" s="14">
+        <v>5</v>
       </c>
       <c r="I21" s="11"/>
     </row>
